--- a/tests/fixtures/sample_wedding.xlsx
+++ b/tests/fixtures/sample_wedding.xlsx
@@ -870,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1189,69 +1189,108 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>H-002</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Guest Jordan Sample</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bride</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>H-003</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Riley</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>O'Placeholder</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Bride</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Riley O'Placeholder</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Riley</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>3 Demo Rd</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Ogdenville</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="S5" t="n">
+      <c r="S6" t="n">
         <v>46203</v>
       </c>
     </row>
